--- a/sports_forms/028_football_equipment_issue_form--sports_forms.xlsx
+++ b/sports_forms/028_football_equipment_issue_form--sports_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -830,8 +830,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="27" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -859,12 +859,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'team_a'}</t>
+          <t>team_a</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Team A'}</t>
+          <t>Team A</t>
         </is>
       </c>
     </row>
@@ -876,12 +876,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'team_b'}</t>
+          <t>team_b</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Team B'}</t>
+          <t>Team B</t>
         </is>
       </c>
     </row>
@@ -893,12 +893,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'team_c'}</t>
+          <t>team_c</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Team C'}</t>
+          <t>Team C</t>
         </is>
       </c>
     </row>
@@ -910,12 +910,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'helmet'}</t>
+          <t>helmet</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Helmet'}</t>
+          <t>Helmet</t>
         </is>
       </c>
     </row>
@@ -927,12 +927,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'cleats'}</t>
+          <t>cleats</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Cleats'}</t>
+          <t>Cleats</t>
         </is>
       </c>
     </row>
@@ -944,12 +944,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'gloves'}</t>
+          <t>gloves</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Gloves'}</t>
+          <t>Gloves</t>
         </is>
       </c>
     </row>
@@ -961,12 +961,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -978,12 +978,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Pending'}</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -995,12 +995,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'assigned'}</t>
+          <t>assigned</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Assigned'}</t>
+          <t>Assigned</t>
         </is>
       </c>
     </row>
@@ -1012,12 +1012,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'returned'}</t>
+          <t>returned</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Returned'}</t>
+          <t>Returned</t>
         </is>
       </c>
     </row>
@@ -1029,12 +1029,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'chatjimmy'}</t>
+          <t>chatjimmy</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'chatjimmy'}</t>
+          <t>chatjimmy</t>
         </is>
       </c>
     </row>
@@ -1046,12 +1046,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'team_jimmy'}</t>
+          <t>team_jimmy</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'team_jimmy'}</t>
+          <t>team jimmy</t>
         </is>
       </c>
     </row>
@@ -1063,12 +1063,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'chatjimmy'}</t>
+          <t>chatjimmy</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'chatjimmy'}</t>
+          <t>chatjimmy</t>
         </is>
       </c>
     </row>
@@ -1097,12 +1097,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'sports_forms'}</t>
+          <t>sports_forms</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Sports Forms'}</t>
+          <t>Sports Forms</t>
         </is>
       </c>
     </row>
